--- a/database_logistik_bpbd_jabar.xlsx
+++ b/database_logistik_bpbd_jabar.xlsx
@@ -346,8 +346,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="tblPermohonanDaerah" displayName="tblPermohonanDaerah" ref="A1:I89" headerRowCount="1">
-  <autoFilter ref="A1:I89"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="tblPermohonanDaerah" displayName="tblPermohonanDaerah" ref="A1:I110" headerRowCount="1">
+  <autoFilter ref="A1:I110"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Nomor Surat Permohonan"/>
     <tableColumn id="2" name="Tahun Anggaran"/>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>Kabupaten Bandung Barat</t>
+          <t>Kabupaten Garut</t>
         </is>
       </c>
       <c r="G25" s="7" t="n"/>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Kabupaten Majalengka</t>
+          <t>Kabupaten Kuningan</t>
         </is>
       </c>
       <c r="G34" s="2" t="n"/>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>Kabupaten Garut</t>
+          <t>Kabupaten Indramayu</t>
         </is>
       </c>
       <c r="G35" s="7" t="n"/>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Kota Bogor</t>
+          <t>Kabupaten Ciamis</t>
         </is>
       </c>
       <c r="G40" s="2" t="n"/>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Kabupaten Sukabumi</t>
+          <t>Kota Cimahi</t>
         </is>
       </c>
       <c r="G52" s="2" t="n"/>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Kabupaten Subang</t>
+          <t>Kota Depok</t>
         </is>
       </c>
       <c r="G56" s="2" t="n"/>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Kabupaten Indramayu</t>
+          <t>Kabupaten Pangandaran</t>
         </is>
       </c>
       <c r="G58" s="2" t="n"/>
@@ -3487,23 +3487,23 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Chainsaw</t>
+          <t>Terpal</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Logistik Lainnya</t>
+          <t>Papan</t>
         </is>
       </c>
       <c r="D64" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>7</v>
+        <v>300</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Kabupaten Bekasi</t>
+          <t>Kabupaten Subang</t>
         </is>
       </c>
       <c r="G64" s="2" t="n"/>
@@ -3513,14 +3513,14 @@
       </c>
       <c r="J64" s="6" t="inlineStr">
         <is>
-          <t>SJ-2025-OUT-0010</t>
+          <t>SJ-2025-OUT-0012</t>
         </is>
       </c>
       <c r="K64" s="4" t="n">
-        <v>4500000</v>
+        <v>150000</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>31500000</v>
+        <v>45000000</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>Kabupaten Karawang</t>
+          <t>Kabupaten Majalengka</t>
         </is>
       </c>
       <c r="G65" s="7" t="n"/>
@@ -3575,23 +3575,23 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Terpal</t>
+          <t>Chainsaw</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Papan</t>
+          <t>Logistik Lainnya</t>
         </is>
       </c>
       <c r="D66" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>300</v>
+        <v>7</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Kabupaten Subang</t>
+          <t>Kota Bekasi</t>
         </is>
       </c>
       <c r="G66" s="2" t="n"/>
@@ -3601,14 +3601,14 @@
       </c>
       <c r="J66" s="6" t="inlineStr">
         <is>
-          <t>SJ-2025-OUT-0012</t>
+          <t>SJ-2025-OUT-0010</t>
         </is>
       </c>
       <c r="K66" s="4" t="n">
-        <v>150000</v>
+        <v>4500000</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>45000000</v>
+        <v>31500000</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>Kabupaten Sukabumi</t>
+          <t>Kabupaten Subang</t>
         </is>
       </c>
       <c r="G75" s="7" t="n"/>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Kota Bandung</t>
+          <t>Kabupaten Cianjur</t>
         </is>
       </c>
       <c r="G80" s="2" t="n"/>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Kota Cimahi</t>
+          <t>Kabupaten Bekasi</t>
         </is>
       </c>
       <c r="G82" s="2" t="n"/>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Kabupaten Indramayu</t>
+          <t>Kabupaten Majalengka</t>
         </is>
       </c>
       <c r="G86" s="2" t="n"/>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Kota Depok</t>
+          <t>Kabupaten Purwakarta</t>
         </is>
       </c>
       <c r="G106" s="2" t="n"/>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="F121" s="7" t="inlineStr">
         <is>
-          <t>Kota Cirebon</t>
+          <t>Kota Bandung</t>
         </is>
       </c>
       <c r="G121" s="7" t="n"/>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>Kota Banjar</t>
+          <t>Kabupaten Indramayu</t>
         </is>
       </c>
       <c r="G123" s="7" t="n"/>
@@ -6307,7 +6307,7 @@
       </c>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>Kota Depok</t>
+          <t>Kabupaten Sukabumi</t>
         </is>
       </c>
       <c r="G127" s="7" t="n"/>
@@ -6617,7 +6617,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>Kabupaten Bogor</t>
+          <t>Kota Cirebon</t>
         </is>
       </c>
       <c r="G134" s="2" t="n"/>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
-          <t>Kota Sukabumi</t>
+          <t>Kabupaten Sumedang</t>
         </is>
       </c>
       <c r="G141" s="7" t="n"/>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="F151" s="7" t="inlineStr">
         <is>
-          <t>Kabupaten Majalengka</t>
+          <t>Kabupaten Bandung Barat</t>
         </is>
       </c>
       <c r="G151" s="7" t="n"/>
@@ -7417,7 +7417,7 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>Kabupaten Karawang</t>
+          <t>Kota Sukabumi</t>
         </is>
       </c>
       <c r="G152" s="2" t="n"/>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="F157" s="7" t="inlineStr">
         <is>
-          <t>Kabupaten Cirebon</t>
+          <t>Kabupaten Sukabumi</t>
         </is>
       </c>
       <c r="G157" s="7" t="n"/>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>Kabupaten Majalengka</t>
+          <t>Kabupaten Purwakarta</t>
         </is>
       </c>
       <c r="G160" s="2" t="n"/>
@@ -7819,7 +7819,7 @@
       </c>
       <c r="F161" s="7" t="inlineStr">
         <is>
-          <t>Kota Tasikmalaya</t>
+          <t>Kabupaten Ciamis</t>
         </is>
       </c>
       <c r="G161" s="7" t="n"/>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="F163" s="7" t="inlineStr">
         <is>
-          <t>Kota Sukabumi</t>
+          <t>Kota Bogor</t>
         </is>
       </c>
       <c r="G163" s="7" t="n"/>
@@ -8483,7 +8483,7 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>Kota Depok</t>
+          <t>Kota Bogor</t>
         </is>
       </c>
       <c r="G176" s="2" t="n"/>
@@ -8527,7 +8527,7 @@
       </c>
       <c r="F177" s="7" t="inlineStr">
         <is>
-          <t>Kabupaten Bekasi</t>
+          <t>Kabupaten Tasikmalaya</t>
         </is>
       </c>
       <c r="G177" s="7" t="n"/>
@@ -8571,7 +8571,7 @@
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>Kabupaten Tasikmalaya</t>
+          <t>Kota Bekasi</t>
         </is>
       </c>
       <c r="G178" s="2" t="n"/>
@@ -8615,7 +8615,7 @@
       </c>
       <c r="F179" s="7" t="inlineStr">
         <is>
-          <t>Kota Bogor</t>
+          <t>Kota Cimahi</t>
         </is>
       </c>
       <c r="G179" s="7" t="n"/>
@@ -8839,7 +8839,7 @@
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>Kabupaten Pangandaran</t>
+          <t>Kota Banjar</t>
         </is>
       </c>
       <c r="G184" s="2" t="n"/>
@@ -9061,7 +9061,7 @@
       </c>
       <c r="F189" s="7" t="inlineStr">
         <is>
-          <t>Kota Bogor</t>
+          <t>Kota Cirebon</t>
         </is>
       </c>
       <c r="G189" s="7" t="n"/>
@@ -9105,7 +9105,7 @@
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>Kota Banjar</t>
+          <t>Kota Tasikmalaya</t>
         </is>
       </c>
       <c r="G190" s="2" t="n"/>
@@ -9369,7 +9369,7 @@
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>Kota Cimahi</t>
+          <t>Kabupaten Bandung</t>
         </is>
       </c>
       <c r="G196" s="2" t="n"/>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="F199" s="7" t="inlineStr">
         <is>
-          <t>Kabupaten Ciamis</t>
+          <t>Kabupaten Pangandaran</t>
         </is>
       </c>
       <c r="G199" s="7" t="n"/>
@@ -9721,7 +9721,7 @@
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>Kabupaten Sukabumi</t>
+          <t>Kabupaten Bogor</t>
         </is>
       </c>
       <c r="G204" s="2" t="n"/>
@@ -9765,7 +9765,7 @@
       </c>
       <c r="F205" s="7" t="inlineStr">
         <is>
-          <t>Kabupaten Tasikmalaya</t>
+          <t>Kota Tasikmalaya</t>
         </is>
       </c>
       <c r="G205" s="7" t="n"/>
@@ -9901,7 +9901,7 @@
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>Kabupaten Majalengka</t>
+          <t>Kabupaten Karawang</t>
         </is>
       </c>
       <c r="G208" s="2" t="n"/>
@@ -10481,7 +10481,7 @@
       </c>
       <c r="F221" s="7" t="inlineStr">
         <is>
-          <t>Kabupaten Purwakarta</t>
+          <t>Kabupaten Tasikmalaya</t>
         </is>
       </c>
       <c r="G221" s="7" t="n"/>
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t>Kota Banjar</t>
+          <t>Kota Sukabumi</t>
         </is>
       </c>
       <c r="G226" s="2" t="n"/>
@@ -10881,7 +10881,7 @@
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t>Kota Cimahi</t>
+          <t>Kota Banjar</t>
         </is>
       </c>
       <c r="G230" s="2" t="n"/>
@@ -11149,7 +11149,7 @@
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
-          <t>Kabupaten Subang</t>
+          <t>Kota Depok</t>
         </is>
       </c>
       <c r="G236" s="2" t="n"/>
@@ -11371,7 +11371,7 @@
       </c>
       <c r="F241" s="7" t="inlineStr">
         <is>
-          <t>Kota Bogor</t>
+          <t>Kabupaten Bandung Barat</t>
         </is>
       </c>
       <c r="G241" s="7" t="n"/>
@@ -11547,7 +11547,7 @@
       </c>
       <c r="F245" s="7" t="inlineStr">
         <is>
-          <t>Kota Bekasi</t>
+          <t>Kabupaten Cirebon</t>
         </is>
       </c>
       <c r="G245" s="7" t="n"/>
@@ -11838,10 +11838,10 @@
     <dataValidation sqref="A2:A251 B2:B61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'_RefData'!$A$2:$A$4</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C251 D2:D61 E2:E89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C251 D2:D61 E2:E110" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'_RefData'!$B$2:$B$5</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D89 E2:E51 F2:F251" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D2:D110 E2:E51 F2:F251" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'_RefData'!$C$2:$C$29</formula1>
     </dataValidation>
   </dataValidations>
@@ -19047,7 +19047,7 @@
     <dataValidation sqref="A2:A251 B2:B61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'_RefData'!$A$2:$A$4</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C251 D2:D61 E2:E89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C251 D2:D61 E2:E110" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'_RefData'!$B$2:$B$5</formula1>
     </dataValidation>
   </dataValidations>
@@ -19146,7 +19146,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Kabupaten Bandung Barat</t>
+          <t>Kabupaten Garut</t>
         </is>
       </c>
       <c r="F2" s="5" t="n">
@@ -19185,7 +19185,7 @@
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>Kabupaten Majalengka</t>
+          <t>Kabupaten Kuningan</t>
         </is>
       </c>
       <c r="F3" s="10" t="n">
@@ -19224,7 +19224,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Kabupaten Garut</t>
+          <t>Kabupaten Indramayu</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
@@ -19263,7 +19263,7 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Kota Bogor</t>
+          <t>Kabupaten Ciamis</t>
         </is>
       </c>
       <c r="F5" s="10" t="n">
@@ -19341,7 +19341,7 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Kabupaten Sukabumi</t>
+          <t>Kota Cimahi</t>
         </is>
       </c>
       <c r="F7" s="10" t="n">
@@ -19380,7 +19380,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Kabupaten Subang</t>
+          <t>Kota Depok</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
@@ -19419,7 +19419,7 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>Kabupaten Indramayu</t>
+          <t>Kabupaten Pangandaran</t>
         </is>
       </c>
       <c r="F9" s="10" t="n">
@@ -19484,20 +19484,20 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Chainsaw</t>
+          <t>Terpal</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Logistik Lainnya</t>
+          <t>Papan</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>7</v>
+        <v>300</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>Kabupaten Bekasi</t>
+          <t>Kabupaten Subang</t>
         </is>
       </c>
       <c r="F11" s="10" t="n">
@@ -19505,14 +19505,14 @@
       </c>
       <c r="G11" s="11" t="inlineStr">
         <is>
-          <t>SJ-2025-OUT-0010</t>
+          <t>SJ-2025-OUT-0012</t>
         </is>
       </c>
       <c r="H11" s="9" t="n">
-        <v>4500000</v>
+        <v>150000</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>31500000</v>
+        <v>45000000</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -19536,7 +19536,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Kabupaten Karawang</t>
+          <t>Kabupaten Majalengka</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
@@ -19562,20 +19562,20 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Terpal</t>
+          <t>Chainsaw</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Papan</t>
+          <t>Logistik Lainnya</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>300</v>
+        <v>7</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>Kabupaten Subang</t>
+          <t>Kota Bekasi</t>
         </is>
       </c>
       <c r="F13" s="10" t="n">
@@ -19583,14 +19583,14 @@
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
-          <t>SJ-2025-OUT-0012</t>
+          <t>SJ-2025-OUT-0010</t>
         </is>
       </c>
       <c r="H13" s="9" t="n">
-        <v>150000</v>
+        <v>4500000</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>45000000</v>
+        <v>31500000</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Kabupaten Sukabumi</t>
+          <t>Kabupaten Subang</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
@@ -19653,7 +19653,7 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>Kota Bandung</t>
+          <t>Kabupaten Cianjur</t>
         </is>
       </c>
       <c r="F15" s="10" t="n">
@@ -19692,7 +19692,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Kota Cimahi</t>
+          <t>Kabupaten Bekasi</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
@@ -19731,7 +19731,7 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>Kabupaten Indramayu</t>
+          <t>Kabupaten Majalengka</t>
         </is>
       </c>
       <c r="F17" s="10" t="n">
@@ -19770,7 +19770,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Kota Depok</t>
+          <t>Kabupaten Purwakarta</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
@@ -19809,7 +19809,7 @@
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>Kota Cirebon</t>
+          <t>Kota Bandung</t>
         </is>
       </c>
       <c r="F19" s="10" t="n">
@@ -19848,7 +19848,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Kota Banjar</t>
+          <t>Kabupaten Indramayu</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
@@ -19926,7 +19926,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Kota Depok</t>
+          <t>Kabupaten Sukabumi</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
@@ -19965,7 +19965,7 @@
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>Kabupaten Bogor</t>
+          <t>Kota Cirebon</t>
         </is>
       </c>
       <c r="F23" s="10" t="n">
@@ -20004,7 +20004,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Kota Sukabumi</t>
+          <t>Kabupaten Sumedang</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
@@ -20043,7 +20043,7 @@
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>Kabupaten Majalengka</t>
+          <t>Kabupaten Bandung Barat</t>
         </is>
       </c>
       <c r="F25" s="10" t="n">
@@ -20082,7 +20082,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Kabupaten Karawang</t>
+          <t>Kota Sukabumi</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
@@ -20121,7 +20121,7 @@
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>Kabupaten Cirebon</t>
+          <t>Kabupaten Sukabumi</t>
         </is>
       </c>
       <c r="F27" s="10" t="n">
@@ -20160,7 +20160,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Kabupaten Majalengka</t>
+          <t>Kabupaten Purwakarta</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
@@ -20199,7 +20199,7 @@
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>Kota Tasikmalaya</t>
+          <t>Kabupaten Ciamis</t>
         </is>
       </c>
       <c r="F29" s="10" t="n">
@@ -20238,7 +20238,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Kota Sukabumi</t>
+          <t>Kota Bogor</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
@@ -20316,7 +20316,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Kota Depok</t>
+          <t>Kota Bogor</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
@@ -20355,7 +20355,7 @@
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>Kabupaten Bekasi</t>
+          <t>Kabupaten Tasikmalaya</t>
         </is>
       </c>
       <c r="F33" s="10" t="n">
@@ -20394,7 +20394,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Kabupaten Tasikmalaya</t>
+          <t>Kota Bekasi</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
@@ -20433,7 +20433,7 @@
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>Kota Bogor</t>
+          <t>Kota Cimahi</t>
         </is>
       </c>
       <c r="F35" s="10" t="n">
@@ -20472,7 +20472,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Kabupaten Pangandaran</t>
+          <t>Kota Banjar</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
@@ -20511,7 +20511,7 @@
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>Kota Bogor</t>
+          <t>Kota Cirebon</t>
         </is>
       </c>
       <c r="F37" s="10" t="n">
@@ -20550,7 +20550,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Kota Banjar</t>
+          <t>Kota Tasikmalaya</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
@@ -20628,7 +20628,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Kota Cimahi</t>
+          <t>Kabupaten Bandung</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
@@ -20667,7 +20667,7 @@
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>Kabupaten Ciamis</t>
+          <t>Kabupaten Pangandaran</t>
         </is>
       </c>
       <c r="F41" s="10" t="n">
@@ -20706,7 +20706,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Kabupaten Sukabumi</t>
+          <t>Kabupaten Bogor</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
@@ -20745,7 +20745,7 @@
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>Kabupaten Tasikmalaya</t>
+          <t>Kota Tasikmalaya</t>
         </is>
       </c>
       <c r="F43" s="10" t="n">
@@ -20784,7 +20784,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Kabupaten Majalengka</t>
+          <t>Kabupaten Karawang</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
@@ -20862,7 +20862,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Kabupaten Purwakarta</t>
+          <t>Kabupaten Tasikmalaya</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
@@ -20901,7 +20901,7 @@
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>Kota Banjar</t>
+          <t>Kota Sukabumi</t>
         </is>
       </c>
       <c r="F47" s="10" t="n">
@@ -20940,7 +20940,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Kota Cimahi</t>
+          <t>Kota Banjar</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
@@ -20979,7 +20979,7 @@
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>Kabupaten Subang</t>
+          <t>Kota Depok</t>
         </is>
       </c>
       <c r="F49" s="10" t="n">
@@ -21018,7 +21018,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Kota Bogor</t>
+          <t>Kabupaten Bandung Barat</t>
         </is>
       </c>
       <c r="F50" s="5" t="n">
@@ -21057,7 +21057,7 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>Kota Bekasi</t>
+          <t>Kabupaten Cirebon</t>
         </is>
       </c>
       <c r="F51" s="10" t="n">
@@ -21101,10 +21101,10 @@
     <dataValidation sqref="A2:A251 B2:B61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'_RefData'!$A$2:$A$4</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C251 D2:D61 E2:E89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C251 D2:D61 E2:E110" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'_RefData'!$B$2:$B$5</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D89 E2:E51 F2:F251" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D2:D110 E2:E51 F2:F251" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'_RefData'!$C$2:$C$29</formula1>
     </dataValidation>
   </dataValidations>
@@ -22994,7 +22994,7 @@
     <dataValidation sqref="A2:A251 B2:B61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'_RefData'!$A$2:$A$4</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C251 D2:D61 E2:E89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C251 D2:D61 E2:E110" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'_RefData'!$B$2:$B$5</formula1>
     </dataValidation>
   </dataValidations>
@@ -24757,7 +24757,7 @@
     <dataValidation sqref="A2:A251 B2:B61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'_RefData'!$A$2:$A$4</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C251 D2:D61 E2:E89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C251 D2:D61 E2:E110" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'_RefData'!$B$2:$B$5</formula1>
     </dataValidation>
   </dataValidations>
@@ -26466,7 +26466,7 @@
     <dataValidation sqref="A2:A251 B2:B61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'_RefData'!$A$2:$A$4</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C251 D2:D61 E2:E89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C251 D2:D61 E2:E110" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'_RefData'!$B$2:$B$5</formula1>
     </dataValidation>
   </dataValidations>
@@ -26483,7 +26483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I90"/>
+  <dimension ref="A1:I111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -26547,18 +26547,18 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>360/001/BPBD-KAB/I/2025</t>
+          <t>360/003/BPBD-KAB/I/2025</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>45677</v>
+        <v>45673</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Kabupaten Bandung</t>
+          <t>Kabupaten Bekasi</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -26572,104 +26572,104 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>760</v>
+        <v>3490</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>15000</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>11400000</v>
+        <v>52350000</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>360/002/BPBD-KAB/I/2025</t>
+          <t>360/004/BPBD-KAB/I/2025</t>
         </is>
       </c>
       <c r="B3" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="C3" s="10" t="n">
-        <v>45677</v>
+        <v>45681</v>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>Kabupaten Bandung</t>
+          <t>Kabupaten Bekasi</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>Sandang</t>
+          <t>Logistik Lainnya</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>Selimut</t>
+          <t>Family Kit</t>
         </is>
       </c>
       <c r="G3" s="9" t="n">
-        <v>760</v>
+        <v>360</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>85000</v>
+        <v>350000</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>64600000</v>
+        <v>126000000</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>360/005/BPBD-KAB/I/2025</t>
+          <t>360/079/BPBD-KAB/I/2025</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>45674</v>
+        <v>45676</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Kabupaten Bandung Barat</t>
+          <t>Kabupaten Ciamis</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Pangan</t>
+          <t>Papan</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Lauk Pauk</t>
+          <t>Terpal</t>
         </is>
       </c>
       <c r="G4" s="4" t="n">
-        <v>480</v>
+        <v>820</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>35000</v>
+        <v>150000</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>16800000</v>
+        <v>123000000</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>360/006/BPBD-KAB/I/2025</t>
+          <t>360/098/BPBD-KAB/I/2025</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>45680</v>
+        <v>45674</v>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Kabupaten Bekasi</t>
+          <t>Kabupaten Cianjur</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
@@ -26679,219 +26679,219 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>Beras</t>
+          <t>Susu Formula</t>
         </is>
       </c>
       <c r="G5" s="9" t="n">
-        <v>3940</v>
+        <v>600</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>15000</v>
+        <v>65000</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>59100000</v>
+        <v>39000000</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>360/007/BPBD-KAB/I/2025</t>
+          <t>360/059/BPBD-KAB/I/2025</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>45679</v>
+        <v>45673</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Kabupaten Bekasi</t>
+          <t>Kabupaten Cirebon</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Logistik Lainnya</t>
+          <t>Pangan</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Chainsaw</t>
+          <t>Susu Formula</t>
         </is>
       </c>
       <c r="G6" s="4" t="n">
-        <v>10</v>
+        <v>840</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>4500000</v>
+        <v>65000</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>45000000</v>
+        <v>54600000</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>360/009/BPBD-KAB/I/2025</t>
+          <t>360/005/BPBD-KAB/I/2025</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>45679</v>
+        <v>45674</v>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Kabupaten Bogor</t>
+          <t>Kabupaten Garut</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Sandang</t>
+          <t>Pangan</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>Pakaian Anak</t>
+          <t>Lauk Pauk</t>
         </is>
       </c>
       <c r="G7" s="9" t="n">
-        <v>820</v>
+        <v>320</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>75000</v>
+        <v>35000</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>61500000</v>
+        <v>11200000</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>360/012/BPBD-KAB/I/2025</t>
+          <t>360/014/BPBD-KAB/I/2025</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>45681</v>
+        <v>45674</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Kabupaten Ciamis</t>
+          <t>Kabupaten Indramayu</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Pangan</t>
+          <t>Papan</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Beras</t>
+          <t>Terpal</t>
         </is>
       </c>
       <c r="G8" s="4" t="n">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>15000</v>
+        <v>150000</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>3600000</v>
+        <v>27000000</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>360/013/BPBD-KAB/I/2025</t>
+          <t>360/015/BPBD-KAB/I/2025</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>45673</v>
+        <v>45679</v>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Kabupaten Ciamis</t>
+          <t>Kabupaten Indramayu</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>Sandang</t>
+          <t>Pangan</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>Selimut</t>
+          <t>Lauk Pauk</t>
         </is>
       </c>
       <c r="G9" s="9" t="n">
-        <v>240</v>
+        <v>1125</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>85000</v>
+        <v>35000</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>20400000</v>
+        <v>39375000</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>360/016/BPBD-KAB/I/2025</t>
+          <t>360/034/BPBD-KAB/I/2025</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>45681</v>
+        <v>45674</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Kabupaten Cianjur</t>
+          <t>Kabupaten Karawang</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Pangan</t>
+          <t>Sandang</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Beras</t>
+          <t>Selimut</t>
         </is>
       </c>
       <c r="G10" s="4" t="n">
-        <v>750</v>
+        <v>1120</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>15000</v>
+        <v>85000</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>11250000</v>
+        <v>95200000</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>360/017/BPBD-KAB/I/2025</t>
+          <t>360/102/BPBD-KAB/I/2025</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="C11" s="10" t="n">
-        <v>45674</v>
+        <v>45672</v>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Kabupaten Cianjur</t>
+          <t>Kabupaten Kuningan</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -26901,108 +26901,108 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>Selimut</t>
+          <t>Matras</t>
         </is>
       </c>
       <c r="G11" s="9" t="n">
-        <v>750</v>
+        <v>530</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>85000</v>
+        <v>120000</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>63750000</v>
+        <v>63600000</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>360/020/BPBD-KAB/I/2025</t>
+          <t>360/044/BPBD-KAB/I/2025</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>45674</v>
+        <v>45677</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Kabupaten Cirebon</t>
+          <t>Kabupaten Majalengka</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Pangan</t>
+          <t>Papan</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Susu Formula</t>
+          <t>Tenda Pengungsi</t>
         </is>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1110</v>
+        <v>90</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>65000</v>
+        <v>8500000</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>72150000</v>
+        <v>765000000</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>360/022/BPBD-KAB/I/2025</t>
+          <t>360/045/BPBD-KAB/I/2025</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>45673</v>
+        <v>45678</v>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Kabupaten Garut</t>
+          <t>Kabupaten Majalengka</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>Papan</t>
+          <t>Sandang</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>Terpal</t>
+          <t>Selimut</t>
         </is>
       </c>
       <c r="G13" s="9" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>150000</v>
+        <v>85000</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>31500000</v>
+        <v>85000000</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>360/024/BPBD-KAB/I/2025</t>
+          <t>360/029/BPBD-KAB/I/2025</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>45680</v>
+        <v>45672</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Kabupaten Indramayu</t>
+          <t>Kabupaten Pangandaran</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -27016,141 +27016,141 @@
         </is>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1260</v>
+        <v>1120</v>
       </c>
       <c r="H14" s="4" t="n">
         <v>25000</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>31500000</v>
+        <v>28000000</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>360/025/BPBD-KAB/I/2025</t>
+          <t>360/054/BPBD-KAB/I/2025</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="C15" s="10" t="n">
-        <v>45672</v>
+        <v>45673</v>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Kabupaten Indramayu</t>
+          <t>Kabupaten Purwakarta</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>Sandang</t>
+          <t>Logistik Lainnya</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>Selimut</t>
+          <t>Family Kit</t>
         </is>
       </c>
       <c r="G15" s="9" t="n">
-        <v>1060</v>
+        <v>880</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>85000</v>
+        <v>350000</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>90100000</v>
+        <v>308000000</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>360/026/BPBD-KAB/I/2025</t>
+          <t>360/009/BPBD-KAB/I/2025</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>45676</v>
+        <v>45681</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Kabupaten Karawang</t>
+          <t>Kabupaten Subang</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Sandang</t>
+          <t>Papan</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Selimut</t>
+          <t>Terpal</t>
         </is>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1670</v>
+        <v>330</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>85000</v>
+        <v>150000</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>141950000</v>
+        <v>49500000</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>360/027/BPBD-KAB/I/2025</t>
+          <t>360/010/BPBD-KAB/I/2025</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="C17" s="10" t="n">
-        <v>45673</v>
+        <v>45680</v>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Kabupaten Karawang</t>
+          <t>Kabupaten Subang</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>Papan</t>
+          <t>Pangan</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>Tenda Pengungsi</t>
+          <t>Makanan Siap Saji</t>
         </is>
       </c>
       <c r="G17" s="9" t="n">
-        <v>130</v>
+        <v>1970</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>8500000</v>
+        <v>45000</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>1105000000</v>
+        <v>88650000</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>360/029/BPBD-KAB/I/2025</t>
+          <t>360/011/BPBD-KAB/I/2025</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>45681</v>
+        <v>45673</v>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Kabupaten Kuningan</t>
+          <t>Kabupaten Sukabumi</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -27160,34 +27160,34 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Beras</t>
+          <t>Biskuit</t>
         </is>
       </c>
       <c r="G18" s="4" t="n">
-        <v>500</v>
+        <v>1680</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>15000</v>
+        <v>25000</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>7500000</v>
+        <v>42000000</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>360/030/BPBD-KAB/I/2025</t>
+          <t>360/106/BPBD-KAB/I/2025</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="C19" s="10" t="n">
-        <v>45678</v>
+        <v>45676</v>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Kabupaten Kuningan</t>
+          <t>Kabupaten Sumedang</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -27197,34 +27197,34 @@
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>Selimut</t>
+          <t>Matras</t>
         </is>
       </c>
       <c r="G19" s="9" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>85000</v>
+        <v>120000</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>42500000</v>
+        <v>64800000</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>360/033/BPBD-KAB/I/2025</t>
+          <t>360/069/BPBD-KOTA/I/2025</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>45673</v>
+        <v>45680</v>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Kabupaten Majalengka</t>
+          <t>Kota Bandung</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -27238,67 +27238,67 @@
         </is>
       </c>
       <c r="G20" s="4" t="n">
-        <v>600</v>
+        <v>840</v>
       </c>
       <c r="H20" s="4" t="n">
         <v>120000</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>72000000</v>
+        <v>100800000</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>360/039/BPBD-KAB/I/2025</t>
+          <t>360/084/BPBD-KOTA/I/2025</t>
         </is>
       </c>
       <c r="B21" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="C21" s="10" t="n">
-        <v>45681</v>
+        <v>45673</v>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Kabupaten Subang</t>
+          <t>Kota Bekasi</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>Sandang</t>
+          <t>Logistik Lainnya</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>Pakaian Anak</t>
+          <t>Chainsaw</t>
         </is>
       </c>
       <c r="G21" s="9" t="n">
-        <v>350</v>
+        <v>10</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>75000</v>
+        <v>4500000</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>26250000</v>
+        <v>45000000</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>360/040/BPBD-KAB/I/2025</t>
+          <t>360/049/BPBD-KOTA/I/2025</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>45677</v>
+        <v>45679</v>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Kabupaten Subang</t>
+          <t>Kota Cimahi</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -27308,71 +27308,71 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Terpal</t>
+          <t>Tenda Keluarga</t>
         </is>
       </c>
       <c r="G22" s="4" t="n">
-        <v>350</v>
+        <v>80</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>150000</v>
+        <v>3200000</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>52500000</v>
+        <v>256000000</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>360/042/BPBD-KAB/I/2025</t>
+          <t>360/064/BPBD-KOTA/I/2025</t>
         </is>
       </c>
       <c r="B23" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="C23" s="10" t="n">
-        <v>45675</v>
+        <v>45680</v>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>Kabupaten Subang</t>
+          <t>Kota Cirebon</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>Pangan</t>
+          <t>Sandang</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>Beras</t>
+          <t>Pakaian Anak</t>
         </is>
       </c>
       <c r="G23" s="9" t="n">
-        <v>0</v>
+        <v>860</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>15000</v>
+        <v>75000</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>0</v>
+        <v>64500000</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>360/043/BPBD-KAB/I/2025</t>
+          <t>360/007/BPBD-KOTA/I/2025</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
         <v>2025</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>45675</v>
+        <v>45680</v>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Kabupaten Subang</t>
+          <t>Kota Depok</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -27382,71 +27382,71 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Selimut</t>
+          <t>Pakaian Anak</t>
         </is>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>85000</v>
+        <v>75000</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0</v>
+        <v>24000000</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>360/045/BPBD-KAB/I/2025</t>
+          <t>360/094/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C25" s="10" t="n">
-        <v>45672</v>
+        <v>46037</v>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>Kabupaten Sukabumi</t>
+          <t>Kabupaten Bandung</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>Papan</t>
+          <t>Sandang</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>Tenda Keluarga</t>
+          <t>Sarung</t>
         </is>
       </c>
       <c r="G25" s="9" t="n">
-        <v>80</v>
+        <v>720</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>3200000</v>
+        <v>60000</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>256000000</v>
+        <v>43200000</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>360/046/BPBD-KAB/I/2025</t>
+          <t>360/095/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>45673</v>
+        <v>46047</v>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Kabupaten Sukabumi</t>
+          <t>Kabupaten Bandung</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -27456,34 +27456,34 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Makanan Siap Saji</t>
+          <t>Beras</t>
         </is>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2150</v>
+        <v>40</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>45000</v>
+        <v>15000</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>96750000</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>360/048/BPBD-KAB/I/2025</t>
+          <t>360/096/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C27" s="10" t="n">
-        <v>45679</v>
+        <v>46043</v>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Kabupaten Sumedang</t>
+          <t>Kabupaten Bandung</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -27493,34 +27493,34 @@
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>Beras</t>
+          <t>Makanan Siap Saji</t>
         </is>
       </c>
       <c r="G27" s="9" t="n">
-        <v>480</v>
+        <v>40</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>15000</v>
+        <v>45000</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>7200000</v>
+        <v>1800000</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>360/049/BPBD-KAB/I/2025</t>
+          <t>360/097/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>45678</v>
+        <v>46040</v>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Kabupaten Sumedang</t>
+          <t>Kabupaten Bandung</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -27534,141 +27534,141 @@
         </is>
       </c>
       <c r="G28" s="4" t="n">
-        <v>480</v>
+        <v>30</v>
       </c>
       <c r="H28" s="4" t="n">
         <v>85000</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>40800000</v>
+        <v>2550000</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>360/054/BPBD-KOTA/I/2025</t>
+          <t>360/074/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C29" s="10" t="n">
-        <v>45678</v>
+        <v>46046</v>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>Kota Bandung</t>
+          <t>Kabupaten Bandung Barat</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>Pangan</t>
+          <t>Sandang</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>Susu Formula</t>
+          <t>Matras</t>
         </is>
       </c>
       <c r="G29" s="9" t="n">
-        <v>670</v>
+        <v>830</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>65000</v>
+        <v>120000</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>43550000</v>
+        <v>99600000</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>360/056/BPBD-KOTA/I/2025</t>
+          <t>360/075/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>45681</v>
+        <v>46037</v>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Kota Bandung</t>
+          <t>Kabupaten Bandung Barat</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Pangan</t>
+          <t>Papan</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Beras</t>
+          <t>Tenda Pengungsi</t>
         </is>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>15000</v>
+        <v>8500000</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0</v>
+        <v>170000000</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>360/057/BPBD-KOTA/I/2025</t>
+          <t>360/076/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C31" s="10" t="n">
-        <v>45682</v>
+        <v>46040</v>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>Kota Bandung</t>
+          <t>Kabupaten Bandung Barat</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>Sandang</t>
+          <t>Pangan</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>Selimut</t>
+          <t>Beras</t>
         </is>
       </c>
       <c r="G31" s="9" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>85000</v>
+        <v>15000</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>0</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>360/060/BPBD-KOTA/I/2025</t>
+          <t>360/077/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>45680</v>
+        <v>46038</v>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Kota Banjar</t>
+          <t>Kabupaten Bandung Barat</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -27678,256 +27678,256 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Lauk Pauk</t>
+          <t>Makanan Siap Saji</t>
         </is>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1320</v>
+        <v>40</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>35000</v>
+        <v>45000</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>46200000</v>
+        <v>1800000</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>360/063/BPBD-KOTA/I/2025</t>
+          <t>360/078/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C33" s="10" t="n">
-        <v>45678</v>
+        <v>46044</v>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>Kota Banjar</t>
+          <t>Kabupaten Bandung Barat</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>Pangan</t>
+          <t>Sandang</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>Beras</t>
+          <t>Selimut</t>
         </is>
       </c>
       <c r="G33" s="9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>15000</v>
+        <v>85000</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>0</v>
+        <v>4250000</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>360/064/BPBD-KOTA/I/2025</t>
+          <t>360/001/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>45672</v>
+        <v>46044</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Kota Banjar</t>
+          <t>Kabupaten Bogor</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Sandang</t>
+          <t>Pangan</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Selimut</t>
+          <t>Air Mineral</t>
         </is>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0</v>
+        <v>3620</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>85000</v>
+        <v>30000</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0</v>
+        <v>108600000</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>360/068/BPBD-KOTA/I/2025</t>
+          <t>360/002/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B35" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C35" s="10" t="n">
-        <v>45675</v>
+        <v>46037</v>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>Kota Bekasi</t>
+          <t>Kabupaten Bogor</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>Pangan</t>
+          <t>Sandang</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>Beras</t>
+          <t>Matras</t>
         </is>
       </c>
       <c r="G35" s="9" t="n">
-        <v>340</v>
+        <v>380</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>15000</v>
+        <v>120000</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>5100000</v>
+        <v>45600000</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>360/069/BPBD-KOTA/I/2025</t>
+          <t>360/080/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>45673</v>
+        <v>46047</v>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Kota Bekasi</t>
+          <t>Kabupaten Ciamis</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Sandang</t>
+          <t>Logistik Lainnya</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Selimut</t>
+          <t>Genset</t>
         </is>
       </c>
       <c r="G36" s="4" t="n">
-        <v>340</v>
+        <v>10</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>85000</v>
+        <v>12500000</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>28900000</v>
+        <v>125000000</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>360/072/BPBD-KOTA/I/2025</t>
+          <t>360/081/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C37" s="10" t="n">
-        <v>45677</v>
+        <v>46046</v>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>Kota Bogor</t>
+          <t>Kabupaten Ciamis</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>Papan</t>
+          <t>Pangan</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>Terpal</t>
+          <t>Beras</t>
         </is>
       </c>
       <c r="G37" s="9" t="n">
-        <v>740</v>
+        <v>40</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>150000</v>
+        <v>15000</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>111000000</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>360/075/BPBD-KOTA/I/2025</t>
+          <t>360/082/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>45672</v>
+        <v>46038</v>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Kota Cimahi</t>
+          <t>Kabupaten Ciamis</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Logistik Lainnya</t>
+          <t>Pangan</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Family Kit</t>
+          <t>Makanan Siap Saji</t>
         </is>
       </c>
       <c r="G38" s="4" t="n">
-        <v>560</v>
+        <v>40</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>350000</v>
+        <v>45000</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>196000000</v>
+        <v>1800000</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>360/078/BPBD-KOTA/I/2025</t>
+          <t>360/083/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B39" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C39" s="10" t="n">
-        <v>45677</v>
+        <v>46044</v>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>Kota Cirebon</t>
+          <t>Kabupaten Ciamis</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
@@ -27937,71 +27937,71 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>Matras</t>
+          <t>Selimut</t>
         </is>
       </c>
       <c r="G39" s="9" t="n">
-        <v>1070</v>
+        <v>40</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>120000</v>
+        <v>85000</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>128400000</v>
+        <v>3400000</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>360/079/BPBD-KOTA/I/2025</t>
+          <t>360/099/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>45672</v>
+        <v>46041</v>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Kota Depok</t>
+          <t>Kabupaten Cianjur</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Logistik Lainnya</t>
+          <t>Pangan</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Family Kit</t>
+          <t>Beras</t>
         </is>
       </c>
       <c r="G40" s="4" t="n">
-        <v>880</v>
+        <v>30</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>350000</v>
+        <v>15000</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>308000000</v>
+        <v>450000</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>360/080/BPBD-KOTA/I/2025</t>
+          <t>360/100/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C41" s="10" t="n">
-        <v>45672</v>
+        <v>46042</v>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>Kota Depok</t>
+          <t>Kabupaten Cianjur</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
@@ -28011,34 +28011,34 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>Biskuit</t>
+          <t>Makanan Siap Saji</t>
         </is>
       </c>
       <c r="G41" s="9" t="n">
-        <v>1790</v>
+        <v>30</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>25000</v>
+        <v>45000</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>44750000</v>
+        <v>1350000</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>360/082/BPBD-KOTA/I/2025</t>
+          <t>360/101/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>45677</v>
+        <v>46043</v>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Kota Sukabumi</t>
+          <t>Kabupaten Cianjur</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -28048,108 +28048,108 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Matras</t>
+          <t>Selimut</t>
         </is>
       </c>
       <c r="G42" s="4" t="n">
-        <v>440</v>
+        <v>30</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>120000</v>
+        <v>85000</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>52800000</v>
+        <v>2550000</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>360/085/BPBD-KOTA/I/2025</t>
+          <t>360/060/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C43" s="10" t="n">
-        <v>45680</v>
+        <v>46041</v>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Kota Tasikmalaya</t>
+          <t>Kabupaten Cirebon</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>Pangan</t>
+          <t>Logistik Lainnya</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>Beras</t>
+          <t>Chainsaw</t>
         </is>
       </c>
       <c r="G43" s="9" t="n">
-        <v>340</v>
+        <v>40</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>15000</v>
+        <v>4500000</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>5100000</v>
+        <v>180000000</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>360/086/BPBD-KOTA/I/2025</t>
+          <t>360/061/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>45681</v>
+        <v>46039</v>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Kota Tasikmalaya</t>
+          <t>Kabupaten Cirebon</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Sandang</t>
+          <t>Pangan</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Selimut</t>
+          <t>Beras</t>
         </is>
       </c>
       <c r="G44" s="4" t="n">
-        <v>340</v>
+        <v>40</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>85000</v>
+        <v>15000</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>28900000</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>360/003/BPBD-KAB/I/2026</t>
+          <t>360/062/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B45" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="C45" s="10" t="n">
-        <v>46039</v>
+        <v>46041</v>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Kabupaten Bandung</t>
+          <t>Kabupaten Cirebon</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
@@ -28163,104 +28163,104 @@
         </is>
       </c>
       <c r="G45" s="9" t="n">
-        <v>760</v>
+        <v>40</v>
       </c>
       <c r="H45" s="9" t="n">
         <v>45000</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>34200000</v>
+        <v>1800000</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>360/004/BPBD-KAB/I/2026</t>
+          <t>360/063/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>46045</v>
+        <v>46044</v>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Kabupaten Bandung</t>
+          <t>Kabupaten Cirebon</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Logistik Lainnya</t>
+          <t>Sandang</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Family Kit</t>
+          <t>Selimut</t>
         </is>
       </c>
       <c r="G46" s="4" t="n">
-        <v>740</v>
+        <v>40</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>350000</v>
+        <v>85000</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>259000000</v>
+        <v>3400000</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>360/008/BPBD-KAB/I/2026</t>
+          <t>360/006/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B47" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="C47" s="10" t="n">
-        <v>46037</v>
+        <v>46047</v>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Kabupaten Bekasi</t>
+          <t>Kabupaten Garut</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>Papan</t>
+          <t>Pangan</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>Tenda Keluarga</t>
+          <t>Air Mineral</t>
         </is>
       </c>
       <c r="G47" s="9" t="n">
-        <v>120</v>
+        <v>2870</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>3200000</v>
+        <v>30000</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>384000000</v>
+        <v>86100000</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>360/010/BPBD-KAB/I/2026</t>
+          <t>360/016/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>46040</v>
+        <v>46045</v>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Kabupaten Bogor</t>
+          <t>Kabupaten Indramayu</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -28270,145 +28270,145 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Air Mineral</t>
+          <t>Beras</t>
         </is>
       </c>
       <c r="G48" s="4" t="n">
-        <v>4150</v>
+        <v>60</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>30000</v>
+        <v>15000</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>124500000</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>360/011/BPBD-KAB/I/2026</t>
+          <t>360/017/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B49" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="C49" s="10" t="n">
-        <v>46047</v>
+        <v>46043</v>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Kabupaten Ciamis</t>
+          <t>Kabupaten Indramayu</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>Papan</t>
+          <t>Pangan</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>Terpal</t>
+          <t>Makanan Siap Saji</t>
         </is>
       </c>
       <c r="G49" s="9" t="n">
-        <v>750</v>
+        <v>60</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>150000</v>
+        <v>45000</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>112500000</v>
+        <v>2700000</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>360/014/BPBD-KAB/I/2026</t>
+          <t>360/018/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>46046</v>
+        <v>46045</v>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Kabupaten Ciamis</t>
+          <t>Kabupaten Indramayu</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Pangan</t>
+          <t>Sandang</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Makanan Siap Saji</t>
+          <t>Selimut</t>
         </is>
       </c>
       <c r="G50" s="4" t="n">
-        <v>240</v>
+        <v>45</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>45000</v>
+        <v>85000</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>10800000</v>
+        <v>3825000</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>360/015/BPBD-KAB/I/2026</t>
+          <t>360/035/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B51" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="C51" s="10" t="n">
-        <v>46045</v>
+        <v>46041</v>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>Kabupaten Ciamis</t>
+          <t>Kabupaten Karawang</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>Logistik Lainnya</t>
+          <t>Papan</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>Family Kit</t>
+          <t>Tenda Keluarga</t>
         </is>
       </c>
       <c r="G51" s="9" t="n">
-        <v>230</v>
+        <v>130</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>350000</v>
+        <v>3200000</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>80500000</v>
+        <v>416000000</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>360/018/BPBD-KAB/I/2026</t>
+          <t>360/036/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>46037</v>
+        <v>46045</v>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Kabupaten Cianjur</t>
+          <t>Kabupaten Karawang</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -28418,108 +28418,108 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Makanan Siap Saji</t>
+          <t>Beras</t>
         </is>
       </c>
       <c r="G52" s="4" t="n">
-        <v>750</v>
+        <v>60</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>45000</v>
+        <v>15000</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>33750000</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>360/019/BPBD-KAB/I/2026</t>
+          <t>360/037/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B53" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="C53" s="10" t="n">
-        <v>46047</v>
+        <v>46046</v>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>Kabupaten Cianjur</t>
+          <t>Kabupaten Karawang</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>Logistik Lainnya</t>
+          <t>Pangan</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>Family Kit</t>
+          <t>Makanan Siap Saji</t>
         </is>
       </c>
       <c r="G53" s="9" t="n">
-        <v>750</v>
+        <v>60</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>350000</v>
+        <v>45000</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>262500000</v>
+        <v>2700000</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>360/021/BPBD-KAB/I/2026</t>
+          <t>360/038/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>46040</v>
+        <v>46039</v>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Kabupaten Cirebon</t>
+          <t>Kabupaten Karawang</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Papan</t>
+          <t>Sandang</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Terpal</t>
+          <t>Matras</t>
         </is>
       </c>
       <c r="G54" s="4" t="n">
-        <v>360</v>
+        <v>70</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>150000</v>
+        <v>120000</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>54000000</v>
+        <v>8400000</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>360/023/BPBD-KAB/I/2026</t>
+          <t>360/103/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B55" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="C55" s="10" t="n">
-        <v>46042</v>
+        <v>46047</v>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>Kabupaten Garut</t>
+          <t>Kabupaten Kuningan</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
@@ -28529,67 +28529,67 @@
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>Air Mineral</t>
+          <t>Beras</t>
         </is>
       </c>
       <c r="G55" s="9" t="n">
-        <v>3200</v>
+        <v>30</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>30000</v>
+        <v>15000</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>96000000</v>
+        <v>450000</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>360/028/BPBD-KAB/I/2026</t>
+          <t>360/104/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="C56" s="5" t="n">
-        <v>46044</v>
+        <v>46037</v>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Kabupaten Karawang</t>
+          <t>Kabupaten Kuningan</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Sandang</t>
+          <t>Pangan</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Pakaian Anak</t>
+          <t>Makanan Siap Saji</t>
         </is>
       </c>
       <c r="G56" s="4" t="n">
-        <v>230</v>
+        <v>30</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>75000</v>
+        <v>45000</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>17250000</v>
+        <v>1350000</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>360/031/BPBD-KAB/I/2026</t>
+          <t>360/105/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B57" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="C57" s="10" t="n">
-        <v>46043</v>
+        <v>46038</v>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
@@ -28598,72 +28598,72 @@
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>Pangan</t>
+          <t>Sandang</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>Makanan Siap Saji</t>
+          <t>Selimut</t>
         </is>
       </c>
       <c r="G57" s="9" t="n">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>45000</v>
+        <v>85000</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>22500000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>360/032/BPBD-KAB/I/2026</t>
+          <t>360/046/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="C58" s="5" t="n">
-        <v>46040</v>
+        <v>46045</v>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Kabupaten Kuningan</t>
+          <t>Kabupaten Majalengka</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Logistik Lainnya</t>
+          <t>Pangan</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Family Kit</t>
+          <t>Beras</t>
         </is>
       </c>
       <c r="G58" s="4" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>350000</v>
+        <v>15000</v>
       </c>
       <c r="I58" s="4" t="n">
-        <v>175000000</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>360/034/BPBD-KAB/I/2026</t>
+          <t>360/047/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B59" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="C59" s="10" t="n">
-        <v>46041</v>
+        <v>46037</v>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
@@ -28672,35 +28672,35 @@
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>Sandang</t>
+          <t>Pangan</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>Matras</t>
+          <t>Makanan Siap Saji</t>
         </is>
       </c>
       <c r="G59" s="9" t="n">
-        <v>1030</v>
+        <v>60</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>120000</v>
+        <v>45000</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>123600000</v>
+        <v>2700000</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>360/035/BPBD-KAB/I/2026</t>
+          <t>360/048/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>46047</v>
+        <v>46039</v>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
@@ -28709,39 +28709,39 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Logistik Lainnya</t>
+          <t>Sandang</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Chainsaw</t>
+          <t>Matras</t>
         </is>
       </c>
       <c r="G60" s="4" t="n">
         <v>50</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>4500000</v>
+        <v>120000</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>225000000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>360/036/BPBD-KAB/I/2026</t>
+          <t>360/030/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B61" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="C61" s="10" t="n">
-        <v>46041</v>
+        <v>46037</v>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>Kabupaten Majalengka</t>
+          <t>Kabupaten Pangandaran</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
@@ -28751,30 +28751,30 @@
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>Tenda Keluarga</t>
+          <t>Terpal</t>
         </is>
       </c>
       <c r="G61" s="9" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>3200000</v>
+        <v>150000</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>608000000</v>
+        <v>24000000</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>360/037/BPBD-KAB/I/2026</t>
+          <t>360/031/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>46042</v>
+        <v>46037</v>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
@@ -28788,108 +28788,108 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>Biskuit</t>
+          <t>Beras</t>
         </is>
       </c>
       <c r="G62" s="4" t="n">
-        <v>1560</v>
+        <v>60</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>25000</v>
+        <v>15000</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>39000000</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>360/038/BPBD-KAB/I/2026</t>
+          <t>360/032/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B63" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="C63" s="10" t="n">
-        <v>46043</v>
+        <v>46047</v>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>Kabupaten Purwakarta</t>
+          <t>Kabupaten Pangandaran</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>Sandang</t>
+          <t>Pangan</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>Pakaian Anak</t>
+          <t>Makanan Siap Saji</t>
         </is>
       </c>
       <c r="G63" s="9" t="n">
-        <v>1550</v>
+        <v>60</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>75000</v>
+        <v>45000</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>116250000</v>
+        <v>2700000</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>360/041/BPBD-KAB/I/2026</t>
+          <t>360/033/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>46037</v>
+        <v>46040</v>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Kabupaten Subang</t>
+          <t>Kabupaten Pangandaran</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Pangan</t>
+          <t>Sandang</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>Makanan Siap Saji</t>
+          <t>Selimut</t>
         </is>
       </c>
       <c r="G64" s="4" t="n">
-        <v>2410</v>
+        <v>70</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>45000</v>
+        <v>85000</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>108450000</v>
+        <v>5950000</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>360/044/BPBD-KAB/I/2026</t>
+          <t>360/055/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B65" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="C65" s="10" t="n">
-        <v>46037</v>
+        <v>46040</v>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>Kabupaten Subang</t>
+          <t>Kabupaten Purwakarta</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
@@ -28899,71 +28899,71 @@
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>Family Kit</t>
+          <t>Chainsaw</t>
         </is>
       </c>
       <c r="G65" s="9" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>350000</v>
+        <v>4500000</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>3500000</v>
+        <v>180000000</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>360/047/BPBD-KAB/I/2026</t>
+          <t>360/056/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>46039</v>
+        <v>46037</v>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Kabupaten Sukabumi</t>
+          <t>Kabupaten Purwakarta</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Sandang</t>
+          <t>Pangan</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>Matras</t>
+          <t>Beras</t>
         </is>
       </c>
       <c r="G66" s="4" t="n">
-        <v>440</v>
+        <v>40</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>120000</v>
+        <v>15000</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>52800000</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>360/050/BPBD-KAB/I/2026</t>
+          <t>360/057/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B67" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="C67" s="10" t="n">
-        <v>46039</v>
+        <v>46041</v>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>Kabupaten Sumedang</t>
+          <t>Kabupaten Purwakarta</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
@@ -28977,326 +28977,326 @@
         </is>
       </c>
       <c r="G67" s="9" t="n">
-        <v>480</v>
+        <v>40</v>
       </c>
       <c r="H67" s="9" t="n">
         <v>45000</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>21600000</v>
+        <v>1800000</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>360/051/BPBD-KAB/I/2026</t>
+          <t>360/058/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="C68" s="5" t="n">
-        <v>46047</v>
+        <v>46038</v>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Kabupaten Sumedang</t>
+          <t>Kabupaten Purwakarta</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Logistik Lainnya</t>
+          <t>Sandang</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>Family Kit</t>
+          <t>Selimut</t>
         </is>
       </c>
       <c r="G68" s="4" t="n">
-        <v>460</v>
+        <v>50</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>350000</v>
+        <v>85000</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>161000000</v>
+        <v>4250000</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>360/052/BPBD-KAB/I/2026</t>
+          <t>360/012/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B69" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="C69" s="10" t="n">
-        <v>46040</v>
+        <v>46042</v>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Kabupaten Tasikmalaya</t>
+          <t>Kabupaten Sukabumi</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>Sandang</t>
+          <t>Papan</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>Selimut</t>
+          <t>Terpal</t>
         </is>
       </c>
       <c r="G69" s="9" t="n">
-        <v>990</v>
+        <v>240</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>85000</v>
+        <v>150000</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>84150000</v>
+        <v>36000000</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>360/053/BPBD-KAB/I/2026</t>
+          <t>360/107/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="C70" s="5" t="n">
-        <v>46041</v>
+        <v>46037</v>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Kabupaten Tasikmalaya</t>
+          <t>Kabupaten Sumedang</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Sandang</t>
+          <t>Pangan</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>Pakaian Dewasa</t>
+          <t>Beras</t>
         </is>
       </c>
       <c r="G70" s="4" t="n">
-        <v>910</v>
+        <v>30</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>95000</v>
+        <v>15000</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>86450000</v>
+        <v>450000</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>360/055/BPBD-KOTA/I/2026</t>
+          <t>360/108/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B71" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="C71" s="10" t="n">
-        <v>46044</v>
+        <v>46041</v>
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>Kota Bandung</t>
+          <t>Kabupaten Sumedang</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>Logistik Lainnya</t>
+          <t>Pangan</t>
         </is>
       </c>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>Chainsaw</t>
+          <t>Makanan Siap Saji</t>
         </is>
       </c>
       <c r="G71" s="9" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>4500000</v>
+        <v>45000</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>90000000</v>
+        <v>1350000</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>360/058/BPBD-KOTA/I/2026</t>
+          <t>360/109/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>46044</v>
+        <v>46043</v>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Kota Bandung</t>
+          <t>Kabupaten Sumedang</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Pangan</t>
+          <t>Sandang</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>Makanan Siap Saji</t>
+          <t>Selimut</t>
         </is>
       </c>
       <c r="G72" s="4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>45000</v>
+        <v>85000</v>
       </c>
       <c r="I72" s="4" t="n">
-        <v>0</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>360/059/BPBD-KOTA/I/2026</t>
+          <t>360/039/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B73" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="C73" s="10" t="n">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>Kota Bandung</t>
+          <t>Kabupaten Tasikmalaya</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>Logistik Lainnya</t>
+          <t>Papan</t>
         </is>
       </c>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>Family Kit</t>
+          <t>Tenda Keluarga</t>
         </is>
       </c>
       <c r="G73" s="9" t="n">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>350000</v>
+        <v>3200000</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>3500000</v>
+        <v>352000000</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>360/061/BPBD-KOTA/I/2026</t>
+          <t>360/040/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="C74" s="5" t="n">
-        <v>46046</v>
+        <v>46043</v>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Kota Banjar</t>
+          <t>Kabupaten Tasikmalaya</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Logistik Lainnya</t>
+          <t>Sandang</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>Perahu Karet</t>
+          <t>Pakaian Anak</t>
         </is>
       </c>
       <c r="G74" s="4" t="n">
-        <v>0</v>
+        <v>1060</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>35000000</v>
+        <v>75000</v>
       </c>
       <c r="I74" s="4" t="n">
-        <v>0</v>
+        <v>79500000</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>360/062/BPBD-KOTA/I/2026</t>
+          <t>360/041/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B75" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="C75" s="10" t="n">
-        <v>46039</v>
+        <v>46043</v>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>Kota Banjar</t>
+          <t>Kabupaten Tasikmalaya</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>Sandang</t>
+          <t>Pangan</t>
         </is>
       </c>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>Pakaian Dewasa</t>
+          <t>Beras</t>
         </is>
       </c>
       <c r="G75" s="9" t="n">
-        <v>1290</v>
+        <v>60</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>95000</v>
+        <v>15000</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>122550000</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>360/065/BPBD-KOTA/I/2026</t>
+          <t>360/042/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="C76" s="5" t="n">
-        <v>46037</v>
+        <v>46040</v>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Kota Banjar</t>
+          <t>Kabupaten Tasikmalaya</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -29310,67 +29310,67 @@
         </is>
       </c>
       <c r="G76" s="4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H76" s="4" t="n">
         <v>45000</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>0</v>
+        <v>2700000</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>360/066/BPBD-KOTA/I/2026</t>
+          <t>360/043/BPBD-KAB/I/2026</t>
         </is>
       </c>
       <c r="B77" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="C77" s="10" t="n">
-        <v>46038</v>
+        <v>46043</v>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>Kota Banjar</t>
+          <t>Kabupaten Tasikmalaya</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>Logistik Lainnya</t>
+          <t>Sandang</t>
         </is>
       </c>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>Family Kit</t>
+          <t>Selimut</t>
         </is>
       </c>
       <c r="G77" s="9" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>350000</v>
+        <v>85000</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>3500000</v>
+        <v>5100000</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>360/067/BPBD-KOTA/I/2026</t>
+          <t>360/070/BPBD-KOTA/I/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="C78" s="5" t="n">
-        <v>46038</v>
+        <v>46041</v>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Kota Bekasi</t>
+          <t>Kota Bandung</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -29384,30 +29384,30 @@
         </is>
       </c>
       <c r="G78" s="4" t="n">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="H78" s="4" t="n">
         <v>4500000</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>675000000</v>
+        <v>90000000</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>360/070/BPBD-KOTA/I/2026</t>
+          <t>360/071/BPBD-KOTA/I/2026</t>
         </is>
       </c>
       <c r="B79" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="C79" s="10" t="n">
-        <v>46047</v>
+        <v>46040</v>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>Kota Bekasi</t>
+          <t>Kota Bandung</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
@@ -29417,54 +29417,54 @@
       </c>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>Makanan Siap Saji</t>
+          <t>Beras</t>
         </is>
       </c>
       <c r="G79" s="9" t="n">
-        <v>340</v>
+        <v>40</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>45000</v>
+        <v>15000</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>15300000</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>360/071/BPBD-KOTA/I/2026</t>
+          <t>360/072/BPBD-KOTA/I/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="C80" s="5" t="n">
-        <v>46042</v>
+        <v>46038</v>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Kota Bekasi</t>
+          <t>Kota Bandung</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Logistik Lainnya</t>
+          <t>Pangan</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>Family Kit</t>
+          <t>Makanan Siap Saji</t>
         </is>
       </c>
       <c r="G80" s="4" t="n">
-        <v>330</v>
+        <v>40</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>350000</v>
+        <v>45000</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>115500000</v>
+        <v>1800000</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
@@ -29477,85 +29477,85 @@
         <v>2026</v>
       </c>
       <c r="C81" s="10" t="n">
-        <v>46047</v>
+        <v>46046</v>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>Kota Bogor</t>
+          <t>Kota Bandung</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>Papan</t>
+          <t>Sandang</t>
         </is>
       </c>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>Seng</t>
+          <t>Selimut</t>
         </is>
       </c>
       <c r="G81" s="9" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>90000</v>
+        <v>85000</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>90000000</v>
+        <v>4250000</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>360/074/BPBD-KOTA/I/2026</t>
+          <t>360/013/BPBD-KOTA/I/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="C82" s="5" t="n">
-        <v>46042</v>
+        <v>46039</v>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Kota Bogor</t>
+          <t>Kota Banjar</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Papan</t>
+          <t>Pangan</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>Tenda Pengungsi</t>
+          <t>Biskuit</t>
         </is>
       </c>
       <c r="G82" s="4" t="n">
-        <v>30</v>
+        <v>1690</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>8500000</v>
+        <v>25000</v>
       </c>
       <c r="I82" s="4" t="n">
-        <v>255000000</v>
+        <v>42250000</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>360/076/BPBD-KOTA/I/2026</t>
+          <t>360/085/BPBD-KOTA/I/2026</t>
         </is>
       </c>
       <c r="B83" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="C83" s="10" t="n">
-        <v>46045</v>
+        <v>46042</v>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>Kota Cimahi</t>
+          <t>Kota Bekasi</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
@@ -29565,34 +29565,34 @@
       </c>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>Sarung</t>
+          <t>Selimut</t>
         </is>
       </c>
       <c r="G83" s="9" t="n">
-        <v>830</v>
+        <v>840</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>60000</v>
+        <v>85000</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>49800000</v>
+        <v>71400000</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>360/077/BPBD-KOTA/I/2026</t>
+          <t>360/086/BPBD-KOTA/I/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="C84" s="5" t="n">
-        <v>46043</v>
+        <v>46037</v>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Kota Cimahi</t>
+          <t>Kota Bekasi</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -29602,23 +29602,23 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>Biskuit</t>
+          <t>Beras</t>
         </is>
       </c>
       <c r="G84" s="4" t="n">
-        <v>320</v>
+        <v>40</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>25000</v>
+        <v>15000</v>
       </c>
       <c r="I84" s="4" t="n">
-        <v>8000000</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>360/081/BPBD-KOTA/I/2026</t>
+          <t>360/087/BPBD-KOTA/I/2026</t>
         </is>
       </c>
       <c r="B85" s="7" t="n">
@@ -29629,207 +29629,984 @@
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>Kota Depok</t>
+          <t>Kota Bekasi</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>Sandang</t>
+          <t>Pangan</t>
         </is>
       </c>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>Sarung</t>
+          <t>Makanan Siap Saji</t>
         </is>
       </c>
       <c r="G85" s="9" t="n">
-        <v>210</v>
+        <v>40</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>60000</v>
+        <v>45000</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>12600000</v>
+        <v>1800000</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>360/083/BPBD-KOTA/I/2026</t>
+          <t>360/088/BPBD-KOTA/I/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="C86" s="5" t="n">
-        <v>46042</v>
+        <v>46040</v>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Kota Sukabumi</t>
+          <t>Kota Bekasi</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Pangan</t>
+          <t>Sandang</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>Biskuit</t>
+          <t>Matras</t>
         </is>
       </c>
       <c r="G86" s="4" t="n">
-        <v>1320</v>
+        <v>40</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>25000</v>
+        <v>120000</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>33000000</v>
+        <v>4800000</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>360/084/BPBD-KOTA/I/2026</t>
+          <t>360/019/BPBD-KOTA/I/2026</t>
         </is>
       </c>
       <c r="B87" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="C87" s="10" t="n">
-        <v>46045</v>
+        <v>46038</v>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>Kota Tasikmalaya</t>
+          <t>Kota Bogor</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>Logistik Lainnya</t>
+          <t>Pangan</t>
         </is>
       </c>
       <c r="F87" s="8" t="inlineStr">
         <is>
-          <t>Genset</t>
+          <t>Biskuit</t>
         </is>
       </c>
       <c r="G87" s="9" t="n">
-        <v>50</v>
+        <v>1130</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>12500000</v>
+        <v>25000</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>625000000</v>
+        <v>28250000</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>360/087/BPBD-KOTA/I/2026</t>
+          <t>360/020/BPBD-KOTA/I/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
         <v>2026</v>
       </c>
       <c r="C88" s="5" t="n">
-        <v>46040</v>
+        <v>46043</v>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Kota Tasikmalaya</t>
+          <t>Kota Bogor</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Pangan</t>
+          <t>Sandang</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>Makanan Siap Saji</t>
+          <t>Sarung</t>
         </is>
       </c>
       <c r="G88" s="4" t="n">
-        <v>340</v>
+        <v>180</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>45000</v>
+        <v>60000</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>15300000</v>
+        <v>10800000</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>360/088/BPBD-KOTA/I/2026</t>
+          <t>360/021/BPBD-KOTA/I/2026</t>
         </is>
       </c>
       <c r="B89" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="C89" s="10" t="n">
+        <v>46043</v>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>Kota Bogor</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>Pangan</t>
+        </is>
+      </c>
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>Beras</t>
+        </is>
+      </c>
+      <c r="G89" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="H89" s="9" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I89" s="9" t="n">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>360/022/BPBD-KOTA/I/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C90" s="5" t="n">
+        <v>46042</v>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>Kota Bogor</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Pangan</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>Makanan Siap Saji</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="H90" s="4" t="n">
+        <v>45000</v>
+      </c>
+      <c r="I90" s="4" t="n">
+        <v>2700000</v>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>360/023/BPBD-KOTA/I/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C91" s="10" t="n">
+        <v>46040</v>
+      </c>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>Kota Bogor</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>Sandang</t>
+        </is>
+      </c>
+      <c r="F91" s="8" t="inlineStr">
+        <is>
+          <t>Selimut</t>
+        </is>
+      </c>
+      <c r="G91" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="H91" s="9" t="n">
+        <v>85000</v>
+      </c>
+      <c r="I91" s="9" t="n">
+        <v>5950000</v>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>360/050/BPBD-KOTA/I/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C92" s="5" t="n">
+        <v>46040</v>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>Kota Cimahi</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Papan</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>Seng</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="n">
+        <v>970</v>
+      </c>
+      <c r="H92" s="4" t="n">
+        <v>90000</v>
+      </c>
+      <c r="I92" s="4" t="n">
+        <v>87300000</v>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>360/051/BPBD-KOTA/I/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C93" s="10" t="n">
+        <v>46039</v>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>Kota Cimahi</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>Pangan</t>
+        </is>
+      </c>
+      <c r="F93" s="8" t="inlineStr">
+        <is>
+          <t>Beras</t>
+        </is>
+      </c>
+      <c r="G93" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="H93" s="9" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I93" s="9" t="n">
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>360/052/BPBD-KOTA/I/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C94" s="5" t="n">
+        <v>46040</v>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>Kota Cimahi</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Pangan</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>Makanan Siap Saji</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="H94" s="4" t="n">
+        <v>45000</v>
+      </c>
+      <c r="I94" s="4" t="n">
+        <v>2250000</v>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>360/053/BPBD-KOTA/I/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C95" s="10" t="n">
+        <v>46047</v>
+      </c>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t>Kota Cimahi</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>Sandang</t>
+        </is>
+      </c>
+      <c r="F95" s="8" t="inlineStr">
+        <is>
+          <t>Selimut</t>
+        </is>
+      </c>
+      <c r="G95" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="H95" s="9" t="n">
+        <v>85000</v>
+      </c>
+      <c r="I95" s="9" t="n">
+        <v>5100000</v>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>360/065/BPBD-KOTA/I/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C96" s="5" t="n">
+        <v>46040</v>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>Kota Cirebon</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Papan</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>Tenda Pengungsi</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H96" s="4" t="n">
+        <v>8500000</v>
+      </c>
+      <c r="I96" s="4" t="n">
+        <v>170000000</v>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>360/066/BPBD-KOTA/I/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C97" s="10" t="n">
+        <v>46041</v>
+      </c>
+      <c r="D97" s="8" t="inlineStr">
+        <is>
+          <t>Kota Cirebon</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>Pangan</t>
+        </is>
+      </c>
+      <c r="F97" s="8" t="inlineStr">
+        <is>
+          <t>Beras</t>
+        </is>
+      </c>
+      <c r="G97" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="H97" s="9" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I97" s="9" t="n">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>360/067/BPBD-KOTA/I/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C98" s="5" t="n">
+        <v>46039</v>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>Kota Cirebon</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Pangan</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>Makanan Siap Saji</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>45000</v>
+      </c>
+      <c r="I98" s="4" t="n">
+        <v>1800000</v>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>360/068/BPBD-KOTA/I/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C99" s="10" t="n">
+        <v>46038</v>
+      </c>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t>Kota Cirebon</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>Sandang</t>
+        </is>
+      </c>
+      <c r="F99" s="8" t="inlineStr">
+        <is>
+          <t>Selimut</t>
+        </is>
+      </c>
+      <c r="G99" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="H99" s="9" t="n">
+        <v>85000</v>
+      </c>
+      <c r="I99" s="9" t="n">
+        <v>4250000</v>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>360/008/BPBD-KOTA/I/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C100" s="5" t="n">
+        <v>46037</v>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>Kota Depok</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Pangan</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>Makanan Siap Saji</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="n">
+        <v>2190</v>
+      </c>
+      <c r="H100" s="4" t="n">
+        <v>45000</v>
+      </c>
+      <c r="I100" s="4" t="n">
+        <v>98550000</v>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>360/024/BPBD-KOTA/I/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C101" s="10" t="n">
+        <v>46038</v>
+      </c>
+      <c r="D101" s="8" t="inlineStr">
+        <is>
+          <t>Kota Sukabumi</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>Sandang</t>
+        </is>
+      </c>
+      <c r="F101" s="8" t="inlineStr">
+        <is>
+          <t>Pakaian Anak</t>
+        </is>
+      </c>
+      <c r="G101" s="9" t="n">
+        <v>150</v>
+      </c>
+      <c r="H101" s="9" t="n">
+        <v>75000</v>
+      </c>
+      <c r="I101" s="9" t="n">
+        <v>11250000</v>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>360/025/BPBD-KOTA/I/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C102" s="5" t="n">
+        <v>46038</v>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>Kota Sukabumi</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Sandang</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>Pakaian Dewasa</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="n">
+        <v>1130</v>
+      </c>
+      <c r="H102" s="4" t="n">
+        <v>95000</v>
+      </c>
+      <c r="I102" s="4" t="n">
+        <v>107350000</v>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t>360/026/BPBD-KOTA/I/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C103" s="10" t="n">
+        <v>46042</v>
+      </c>
+      <c r="D103" s="8" t="inlineStr">
+        <is>
+          <t>Kota Sukabumi</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>Pangan</t>
+        </is>
+      </c>
+      <c r="F103" s="8" t="inlineStr">
+        <is>
+          <t>Beras</t>
+        </is>
+      </c>
+      <c r="G103" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="H103" s="9" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I103" s="9" t="n">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>360/027/BPBD-KOTA/I/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C104" s="5" t="n">
+        <v>46041</v>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>Kota Sukabumi</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Pangan</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>Makanan Siap Saji</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="H104" s="4" t="n">
+        <v>45000</v>
+      </c>
+      <c r="I104" s="4" t="n">
+        <v>2700000</v>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>360/028/BPBD-KOTA/I/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C105" s="10" t="n">
+        <v>46045</v>
+      </c>
+      <c r="D105" s="8" t="inlineStr">
+        <is>
+          <t>Kota Sukabumi</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>Sandang</t>
+        </is>
+      </c>
+      <c r="F105" s="8" t="inlineStr">
+        <is>
+          <t>Selimut</t>
+        </is>
+      </c>
+      <c r="G105" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="H105" s="9" t="n">
+        <v>85000</v>
+      </c>
+      <c r="I105" s="9" t="n">
+        <v>5950000</v>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>360/089/BPBD-KOTA/I/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C106" s="5" t="n">
         <v>46044</v>
       </c>
-      <c r="D89" s="8" t="inlineStr">
+      <c r="D106" s="3" t="inlineStr">
         <is>
           <t>Kota Tasikmalaya</t>
         </is>
       </c>
-      <c r="E89" s="7" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Logistik Lainnya</t>
         </is>
       </c>
-      <c r="F89" s="8" t="inlineStr">
-        <is>
-          <t>Family Kit</t>
-        </is>
-      </c>
-      <c r="G89" s="9" t="n">
-        <v>330</v>
-      </c>
-      <c r="H89" s="9" t="n">
-        <v>350000</v>
-      </c>
-      <c r="I89" s="9" t="n">
-        <v>115500000</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="12" t="inlineStr">
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>Perahu Karet</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" s="4" t="n">
+        <v>35000000</v>
+      </c>
+      <c r="I106" s="4" t="n">
+        <v>35000000</v>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>360/090/BPBD-KOTA/I/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C107" s="10" t="n">
+        <v>46042</v>
+      </c>
+      <c r="D107" s="8" t="inlineStr">
+        <is>
+          <t>Kota Tasikmalaya</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>Sandang</t>
+        </is>
+      </c>
+      <c r="F107" s="8" t="inlineStr">
+        <is>
+          <t>Pakaian Dewasa</t>
+        </is>
+      </c>
+      <c r="G107" s="9" t="n">
+        <v>780</v>
+      </c>
+      <c r="H107" s="9" t="n">
+        <v>95000</v>
+      </c>
+      <c r="I107" s="9" t="n">
+        <v>74100000</v>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>360/091/BPBD-KOTA/I/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C108" s="5" t="n">
+        <v>46045</v>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>Kota Tasikmalaya</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Pangan</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>Beras</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="H108" s="4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I108" s="4" t="n">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="7" t="inlineStr">
+        <is>
+          <t>360/092/BPBD-KOTA/I/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C109" s="10" t="n">
+        <v>46046</v>
+      </c>
+      <c r="D109" s="8" t="inlineStr">
+        <is>
+          <t>Kota Tasikmalaya</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="inlineStr">
+        <is>
+          <t>Pangan</t>
+        </is>
+      </c>
+      <c r="F109" s="8" t="inlineStr">
+        <is>
+          <t>Makanan Siap Saji</t>
+        </is>
+      </c>
+      <c r="G109" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="H109" s="9" t="n">
+        <v>45000</v>
+      </c>
+      <c r="I109" s="9" t="n">
+        <v>1800000</v>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>360/093/BPBD-KOTA/I/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C110" s="5" t="n">
+        <v>46039</v>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>Kota Tasikmalaya</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Sandang</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>Selimut</t>
+        </is>
+      </c>
+      <c r="G110" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="H110" s="4" t="n">
+        <v>85000</v>
+      </c>
+      <c r="I110" s="4" t="n">
+        <v>3315000</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="12" t="inlineStr">
         <is>
           <t>TOTAL PERMOHONAN PENGUATAN</t>
         </is>
       </c>
-      <c r="B90" s="13" t="n"/>
-      <c r="C90" s="13" t="n"/>
-      <c r="D90" s="13" t="n"/>
-      <c r="E90" s="13" t="n"/>
-      <c r="F90" s="13" t="n"/>
-      <c r="G90" s="14">
-        <f>SUM(G2:G89)</f>
+      <c r="B111" s="13" t="n"/>
+      <c r="C111" s="13" t="n"/>
+      <c r="D111" s="13" t="n"/>
+      <c r="E111" s="13" t="n"/>
+      <c r="F111" s="13" t="n"/>
+      <c r="G111" s="14">
+        <f>SUM(G2:G110)</f>
         <v/>
       </c>
-      <c r="H90" s="13" t="n"/>
-      <c r="I90" s="14">
-        <f>SUM(I2:I89)</f>
+      <c r="H111" s="13" t="n"/>
+      <c r="I111" s="14">
+        <f>SUM(I2:I110)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation sqref="B2:B89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B110" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'_RefData'!$D$2:$D$3</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C251 D2:D61 E2:E89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C251 D2:D61 E2:E110" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'_RefData'!$B$2:$B$5</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D89 E2:E51 F2:F251" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D2:D110 E2:E51 F2:F251" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'_RefData'!$C$2:$C$29</formula1>
     </dataValidation>
   </dataValidations>
